--- a/outputs/monitor_xlsx/20260225.xlsx
+++ b/outputs/monitor_xlsx/20260225.xlsx
@@ -999,7 +999,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V26"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2322,7 +2322,7 @@
         <v>-106280</v>
       </c>
       <c r="N25" t="n">
-        <v>18.98</v>
+        <v>15.46</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2380,6 +2380,59 @@
       <c r="O26" t="inlineStr">
         <is>
           <t>偏多</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="E27" t="n">
+        <v>530</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>119</v>
+      </c>
+      <c r="G27" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-70</v>
+      </c>
+      <c r="J27" t="n">
+        <v>19</v>
+      </c>
+      <c r="K27" t="n">
+        <v>333</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1732</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-8884</v>
+      </c>
+      <c r="N27" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>中性</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260225.xlsx
+++ b/outputs/monitor_xlsx/20260225.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -526,215 +526,236 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>美債10年殖利率</t>
+          <t>加權指數 (TWII)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>35413.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+0.42%</t>
-        </is>
-      </c>
+          <t>+2.05%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>總經</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>黃金指數 (GC=F)</t>
+          <t>櫃買指數 (OTC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5199.4$</t>
+          <t>313.24</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+0.85%</t>
-        </is>
-      </c>
+          <t>+0.58%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>貨幣</t>
+          <t>大盤</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>美元/台幣匯率</t>
+          <t>台指近月期貨</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.38</t>
+          <t>35490.0</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17%</t>
-        </is>
-      </c>
+          <t>+1.87%</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>現貨</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>費半指數 (SOX)</t>
+          <t>美債10年殖利率</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>8467.43</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+1.62%</t>
-        </is>
-      </c>
+          <t>+0.42%</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>情緒</t>
+          <t>總經</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>恐慌指數 (VIX)</t>
+          <t>黃金指數 (GC=F)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>17.93</t>
+          <t>5206.4$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-8.29%</t>
-        </is>
-      </c>
+          <t>+0.98%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>貨幣</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>外資現貨</t>
+          <t>美元/台幣匯率</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>411.48億</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>440.61億</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2203.05億</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>47.68億</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>953.63億</t>
-        </is>
-      </c>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>-0.17%</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>現貨</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>投信現貨</t>
+          <t>費半指數 (SOX)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>51.2億</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>36.08億</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>180.41億</t>
-        </is>
-      </c>
+          <t>8467.43</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+1.62%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>情緒</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>選擇權 P/C Ratio</t>
+          <t>恐慌指數 (VIX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>182.17%</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>178.47%</t>
-        </is>
-      </c>
+          <t>17.93</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>-8.29%</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>籌碼</t>
+          <t>原物料</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>三大法人合計</t>
+          <t>WTI原油期貨</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>424.38億</t>
-        </is>
-      </c>
+          <t>65.42$</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>-0.32%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -744,54 +765,175 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>外資期貨未平倉</t>
+          <t>外資現貨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>12782口</t>
-        </is>
-      </c>
+          <t>411.48億</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>None口</t>
+          <t>440.61億</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2203.05億</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>73.96億</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1479.26億</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>投信現貨</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>51.2億</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>36.08億</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>180.41億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>選擇權 P/C Ratio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>三大法人合計</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>424.38億</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>籌碼</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>外資期貨未平倉</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>12782口</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>13404口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>結算</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>融資融券變化</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>-58.99億</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
         <is>
           <t>-22.69億</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>-113.45億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>-12.59億</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-251.74億</t>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>None億</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -862,7 +1004,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>47.68億</t>
+          <t>73.96億</t>
         </is>
       </c>
     </row>
@@ -874,9 +1016,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>953.63億</t>
-        </is>
-      </c>
+          <t>1479.26億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -941,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-12.59億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -953,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-251.74億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -972,7 +1118,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>178.47%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -984,7 +1130,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>None口</t>
+          <t>13404口</t>
         </is>
       </c>
     </row>
@@ -999,20 +1145,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
@@ -1033,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1047,67 +1192,67 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
+          <t>市場別</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>漲跌幅(%)</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>成交量(張)</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>外資當日(張)</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>外資5日累計</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>投信當日(張)</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>投信5日累計</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>自營商當日(張)</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>融資增減(張)</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>融資5日累計</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>借券增減(張)</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>MA20乖離(%)</t>
-        </is>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>籌碼評價</t>
         </is>
       </c>
       <c r="P3" s="5" t="inlineStr">
@@ -1157,43 +1302,43 @@
           <t>0050</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>81.09999999999999</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>2.14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>167423</v>
       </c>
-      <c r="F4" s="6" t="n">
+      <c r="G4" s="6" t="n">
         <v>-36864</v>
       </c>
-      <c r="G4" t="n">
-        <v>-98604</v>
-      </c>
       <c r="H4" t="n">
+        <v>-74057</v>
+      </c>
+      <c r="I4" t="n">
         <v>5000</v>
       </c>
-      <c r="I4" t="n">
-        <v>16700</v>
-      </c>
       <c r="J4" t="n">
+        <v>29726</v>
+      </c>
+      <c r="K4" t="n">
         <v>65465</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>8333</v>
       </c>
-      <c r="L4" t="n">
-        <v>15205</v>
-      </c>
       <c r="M4" t="n">
+        <v>29786</v>
+      </c>
+      <c r="N4" t="n">
         <v>-4080148</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1204,39 +1349,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00708L</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S&amp;P黃金正2</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-352</v>
+          <t>華城</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1050</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="F5" t="n">
+        <v>7231</v>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>1236</v>
+      </c>
+      <c r="H5" t="n">
+        <v>651</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>297</v>
       </c>
       <c r="J5" t="n">
-        <v>1091</v>
+        <v>-1094</v>
       </c>
       <c r="K5" t="n">
-        <v>9650</v>
+        <v>138</v>
       </c>
       <c r="L5" t="n">
-        <v>19975</v>
+        <v>3176</v>
       </c>
       <c r="M5" t="n">
-        <v>-28156</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
+        <v>11595</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-78718</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1247,51 +1404,51 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>華城</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="E6" t="n">
-        <v>7231</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>1236</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-70</v>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1435</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14709</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>708</v>
       </c>
       <c r="H6" t="n">
-        <v>297</v>
+        <v>4175</v>
       </c>
       <c r="I6" t="n">
-        <v>-516</v>
+        <v>421</v>
       </c>
       <c r="J6" t="n">
-        <v>138</v>
+        <v>1771</v>
       </c>
       <c r="K6" t="n">
-        <v>3176</v>
+        <v>352</v>
       </c>
       <c r="L6" t="n">
-        <v>5882</v>
+        <v>6634</v>
       </c>
       <c r="M6" t="n">
-        <v>-78718</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
+        <v>25896</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-648645</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1302,51 +1459,51 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>台達電</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>1435</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="E7" t="n">
-        <v>14709</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>708</v>
-      </c>
-      <c r="G7" t="n">
-        <v>3659</v>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="F7" t="n">
+        <v>47398</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-4192</v>
       </c>
       <c r="H7" t="n">
-        <v>421</v>
+        <v>-2979</v>
       </c>
       <c r="I7" t="n">
-        <v>1078</v>
+        <v>2744</v>
       </c>
       <c r="J7" t="n">
-        <v>352</v>
+        <v>5189</v>
       </c>
       <c r="K7" t="n">
-        <v>6634</v>
+        <v>942</v>
       </c>
       <c r="L7" t="n">
-        <v>13199</v>
+        <v>21635</v>
       </c>
       <c r="M7" t="n">
-        <v>-648645</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
+        <v>85446</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-6482895</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1357,51 +1514,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>台積電</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2015</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E8" t="n">
-        <v>47398</v>
-      </c>
-      <c r="F8" s="6" t="n">
-        <v>-4192</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-10671</v>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1450</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4862</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>2744</v>
+        <v>1779</v>
       </c>
       <c r="I8" t="n">
-        <v>3808</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>942</v>
+        <v>1355</v>
       </c>
       <c r="K8" t="n">
-        <v>21635</v>
+        <v>59</v>
       </c>
       <c r="L8" t="n">
-        <v>42927</v>
+        <v>1780</v>
       </c>
       <c r="M8" t="n">
-        <v>-6482895</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+        <v>7888</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-140150</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1412,51 +1569,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>華邦電</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>118</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="E9" t="n">
-        <v>171060</v>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>-17046</v>
-      </c>
-      <c r="G9" t="n">
-        <v>-3360</v>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3934</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-614</v>
       </c>
       <c r="H9" t="n">
-        <v>6898</v>
+        <v>-488</v>
       </c>
       <c r="I9" t="n">
-        <v>15498</v>
+        <v>405</v>
       </c>
       <c r="J9" t="n">
-        <v>2859</v>
+        <v>460</v>
       </c>
       <c r="K9" t="n">
-        <v>137867</v>
+        <v>64</v>
       </c>
       <c r="L9" t="n">
-        <v>279157</v>
+        <v>1544</v>
       </c>
       <c r="M9" t="n">
-        <v>-1111388</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+        <v>3869</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-106280</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1475,43 +1632,43 @@
           <t>台光電</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>2420</v>
       </c>
-      <c r="D10" s="6" t="n">
+      <c r="E10" s="6" t="n">
         <v>4.76</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>3740</v>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="G10" s="6" t="n">
         <v>-170</v>
       </c>
-      <c r="G10" t="n">
-        <v>-235</v>
-      </c>
       <c r="H10" t="n">
+        <v>-1365</v>
+      </c>
+      <c r="I10" t="n">
         <v>74</v>
       </c>
-      <c r="I10" t="n">
-        <v>529</v>
-      </c>
       <c r="J10" t="n">
+        <v>1492</v>
+      </c>
+      <c r="K10" t="n">
         <v>57</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>2084</v>
       </c>
-      <c r="L10" t="n">
-        <v>4441</v>
-      </c>
       <c r="M10" t="n">
+        <v>8739</v>
+      </c>
+      <c r="N10" t="n">
         <v>-89463</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1522,51 +1679,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>3480</v>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1723</v>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G11" t="n">
-        <v>268</v>
+          <t>光聖</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2080</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="F11" t="n">
+        <v>985</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>120</v>
+        <v>359</v>
       </c>
       <c r="I11" t="n">
-        <v>-104</v>
+        <v>-4</v>
       </c>
       <c r="J11" t="n">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="K11" t="n">
-        <v>5834</v>
+        <v>16</v>
       </c>
       <c r="L11" t="n">
-        <v>11770</v>
+        <v>4186</v>
       </c>
       <c r="M11" t="n">
-        <v>-19717</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
+        <v>16807</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-19156</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1577,51 +1734,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>205.5</v>
-      </c>
-      <c r="D12" s="7" t="n">
-        <v>-2.84</v>
-      </c>
-      <c r="E12" t="n">
-        <v>37070</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>-5807</v>
-      </c>
-      <c r="G12" t="n">
-        <v>-1088</v>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>4.93</v>
+      </c>
+      <c r="F12" t="n">
+        <v>530</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>119</v>
       </c>
       <c r="H12" t="n">
-        <v>2249</v>
+        <v>-112</v>
       </c>
       <c r="I12" t="n">
-        <v>2493</v>
+        <v>-6</v>
       </c>
       <c r="J12" t="n">
-        <v>1048</v>
+        <v>-64</v>
       </c>
       <c r="K12" t="n">
-        <v>23101</v>
+        <v>19</v>
       </c>
       <c r="L12" t="n">
-        <v>48324</v>
+        <v>333</v>
       </c>
       <c r="M12" t="n">
-        <v>-267357</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
+        <v>1399</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-8884</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1632,51 +1789,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>光聖</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>2080</v>
-      </c>
-      <c r="D13" s="6" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E13" t="n">
-        <v>985</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>19</v>
-      </c>
-      <c r="G13" t="n">
-        <v>63</v>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2315</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2730</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-52</v>
       </c>
       <c r="H13" t="n">
-        <v>-4</v>
+        <v>-232</v>
       </c>
       <c r="I13" t="n">
-        <v>54</v>
+        <v>-70</v>
       </c>
       <c r="J13" t="n">
-        <v>16</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
-        <v>4186</v>
+        <v>14</v>
       </c>
       <c r="L13" t="n">
-        <v>8454</v>
+        <v>-210</v>
       </c>
       <c r="M13" t="n">
-        <v>-19156</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
+        <v>-70</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1687,51 +1844,51 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>聯亞</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>1265</v>
+          <t>華星光</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
       </c>
       <c r="D14" t="n">
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3871</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>399</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1025</v>
+      </c>
+      <c r="I14" t="n">
+        <v>581</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2372</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-236</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-906</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-1755</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
-      </c>
-      <c r="E14" t="n">
-        <v>606</v>
-      </c>
-      <c r="F14" s="6" t="n">
-        <v>-52</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-162</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-70</v>
-      </c>
-      <c r="I14" t="n">
-        <v>42</v>
-      </c>
-      <c r="J14" t="n">
-        <v>14</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-210</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-15</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1742,51 +1899,48 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>威剛</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>298</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>-4.79</v>
-      </c>
-      <c r="E15" t="n">
-        <v>20502</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>-8822</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-179</v>
+          <t>萬潤</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>974</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>9.93</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1350</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>2060</v>
       </c>
       <c r="H15" t="n">
-        <v>-1148</v>
-      </c>
-      <c r="I15" t="n">
-        <v>82</v>
+        <v>7941</v>
       </c>
       <c r="J15" t="n">
-        <v>-668</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>1123</v>
+        <v>-93</v>
       </c>
       <c r="L15" t="n">
-        <v>-288</v>
+        <v>-299</v>
       </c>
       <c r="M15" t="n">
+        <v>-399</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1797,642 +1951,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3265</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>台新科</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>145</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1661</v>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>-41</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1408</v>
+          <t>均華</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1600</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="F16" t="n">
+        <v>904</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-35</v>
       </c>
       <c r="H16" t="n">
-        <v>-3</v>
-      </c>
-      <c r="I16" t="n">
+        <v>-61</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-85</v>
+      </c>
+      <c r="K16" t="n">
+        <v>37</v>
+      </c>
+      <c r="L16" t="n">
+        <v>24</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-15</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="J16" t="n">
-        <v>-64</v>
-      </c>
-      <c r="K16" t="n">
-        <v>45</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-60</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>4979</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華星光</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>405</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="E17" t="n">
-        <v>27452</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>399</v>
-      </c>
-      <c r="G17" t="n">
-        <v>4388</v>
-      </c>
-      <c r="H17" t="n">
-        <v>581</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1952</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-236</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-906</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-575</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>3189</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>景碩</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>325.5</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>61480</v>
-      </c>
-      <c r="F18" s="6" t="n">
-        <v>-377</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-936</v>
-      </c>
-      <c r="H18" t="n">
-        <v>930</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1019</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2392</v>
-      </c>
-      <c r="K18" t="n">
-        <v>19000</v>
-      </c>
-      <c r="L18" t="n">
-        <v>40307</v>
-      </c>
-      <c r="M18" t="n">
-        <v>-113337</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>4060</v>
-      </c>
-      <c r="D19" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2922</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>342</v>
-      </c>
-      <c r="G19" t="n">
-        <v>567</v>
-      </c>
-      <c r="H19" t="n">
-        <v>93</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-34</v>
-      </c>
-      <c r="J19" t="n">
-        <v>124</v>
-      </c>
-      <c r="K19" t="n">
-        <v>2047</v>
-      </c>
-      <c r="L19" t="n">
-        <v>11617</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-46414</v>
-      </c>
-      <c r="N19" t="n">
-        <v>10.87</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3138</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>耀登</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>180</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E20" t="n">
-        <v>6584</v>
-      </c>
-      <c r="F20" s="6" t="n">
-        <v>-85</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-1689</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>57</v>
-      </c>
-      <c r="K20" t="n">
-        <v>4399</v>
-      </c>
-      <c r="L20" t="n">
-        <v>21902</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-11355</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>1035</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>5.61</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4697</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>737</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2024</v>
-      </c>
-      <c r="H21" t="n">
-        <v>201</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-272</v>
-      </c>
-      <c r="J21" t="n">
-        <v>120</v>
-      </c>
-      <c r="K21" t="n">
-        <v>2406</v>
-      </c>
-      <c r="L21" t="n">
-        <v>12109</v>
-      </c>
-      <c r="M21" t="n">
-        <v>-47589</v>
-      </c>
-      <c r="N21" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2345</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>智邦</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>1450</v>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E22" t="n">
-        <v>4862</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="G22" t="n">
-        <v>1794</v>
-      </c>
-      <c r="H22" t="n">
-        <v>4</v>
-      </c>
-      <c r="I22" t="n">
-        <v>1359</v>
-      </c>
-      <c r="J22" t="n">
-        <v>59</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1780</v>
-      </c>
-      <c r="L22" t="n">
-        <v>9668</v>
-      </c>
-      <c r="M22" t="n">
-        <v>-140150</v>
-      </c>
-      <c r="N22" t="n">
-        <v>17.67</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>均華</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>962</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="E23" t="n">
-        <v>826</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>-35</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-96</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-85</v>
-      </c>
-      <c r="J23" t="n">
-        <v>37</v>
-      </c>
-      <c r="K23" t="n">
-        <v>24</v>
-      </c>
-      <c r="L23" t="n">
-        <v>9</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>624</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2040</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>2060</v>
-      </c>
-      <c r="G24" t="n">
-        <v>10001</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-93</v>
-      </c>
-      <c r="K24" t="n">
-        <v>-299</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-698</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>1255</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="E25" t="n">
-        <v>3934</v>
-      </c>
-      <c r="F25" s="6" t="n">
-        <v>-614</v>
-      </c>
-      <c r="G25" t="n">
-        <v>-1102</v>
-      </c>
-      <c r="H25" t="n">
-        <v>405</v>
-      </c>
-      <c r="I25" t="n">
-        <v>865</v>
-      </c>
-      <c r="J25" t="n">
-        <v>64</v>
-      </c>
-      <c r="K25" t="n">
-        <v>1544</v>
-      </c>
-      <c r="L25" t="n">
-        <v>5413</v>
-      </c>
-      <c r="M25" t="n">
-        <v>-106280</v>
-      </c>
-      <c r="N25" t="n">
-        <v>15.46</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E26" t="n">
-        <v>3691</v>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>-174</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1850</v>
-      </c>
-      <c r="H26" t="n">
-        <v>46</v>
-      </c>
-      <c r="I26" t="n">
-        <v>30</v>
-      </c>
-      <c r="J26" t="n">
-        <v>111</v>
-      </c>
-      <c r="K26" t="n">
-        <v>6329</v>
-      </c>
-      <c r="L26" t="n">
-        <v>29911</v>
-      </c>
-      <c r="M26" t="n">
-        <v>-58851</v>
-      </c>
-      <c r="N26" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="E27" t="n">
-        <v>530</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>119</v>
-      </c>
-      <c r="G27" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-6</v>
-      </c>
-      <c r="I27" t="n">
-        <v>-70</v>
-      </c>
-      <c r="J27" t="n">
-        <v>19</v>
-      </c>
-      <c r="K27" t="n">
-        <v>333</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1732</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-8884</v>
-      </c>
-      <c r="N27" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>中性</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260225.xlsx
+++ b/outputs/monitor_xlsx/20260225.xlsx
@@ -544,10 +544,6 @@
           <t>+2.05%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>+0.58%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+1.87%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+0.42%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>+0.98%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.17%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>+1.62%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>-8.29%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>-0.32%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>411.48億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>440.61億</t>
@@ -811,7 +774,6 @@
           <t>51.2億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>36.08億</t>
@@ -822,8 +784,6 @@
           <t>180.41億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>424.38億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>12782口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13404口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>-58.99億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-22.69億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1998,6 +1942,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>295</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1528</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>367</v>
+      </c>
+      <c r="G17" t="n">
+        <v>7721</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>737</v>
+      </c>
+      <c r="J17" t="n">
+        <v>56</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6510</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31546</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-21409</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.46</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260225.xlsx
+++ b/outputs/monitor_xlsx/20260225.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>2.14</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>167423</v>
       </c>
       <c r="G4" s="6" t="n">
         <v>-36864</v>
       </c>
       <c r="H4" t="n">
-        <v>-74057</v>
+        <v>-110922</v>
       </c>
       <c r="I4" t="n">
         <v>5000</v>
       </c>
       <c r="J4" t="n">
-        <v>29726</v>
+        <v>34726</v>
       </c>
       <c r="K4" t="n">
         <v>65465</v>
@@ -1279,11 +1278,14 @@
         <v>8333</v>
       </c>
       <c r="M4" t="n">
-        <v>29786</v>
+        <v>38119</v>
       </c>
       <c r="N4" t="n">
         <v>-4080148</v>
       </c>
+      <c r="O4" t="n">
+        <v>9.58</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>1050</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>9.83</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>7231</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>1236</v>
       </c>
       <c r="H5" t="n">
-        <v>651</v>
+        <v>1887</v>
       </c>
       <c r="I5" t="n">
         <v>297</v>
       </c>
       <c r="J5" t="n">
-        <v>-1094</v>
+        <v>-797</v>
       </c>
       <c r="K5" t="n">
         <v>138</v>
@@ -1334,11 +1336,14 @@
         <v>3176</v>
       </c>
       <c r="M5" t="n">
-        <v>11595</v>
+        <v>14771</v>
       </c>
       <c r="N5" t="n">
         <v>-78718</v>
       </c>
+      <c r="O5" t="n">
+        <v>6.09</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1435</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>3.61</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>14709</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>708</v>
       </c>
       <c r="H6" t="n">
-        <v>4175</v>
+        <v>4884</v>
       </c>
       <c r="I6" t="n">
         <v>421</v>
       </c>
       <c r="J6" t="n">
-        <v>1771</v>
+        <v>2192</v>
       </c>
       <c r="K6" t="n">
         <v>352</v>
@@ -1389,11 +1394,14 @@
         <v>6634</v>
       </c>
       <c r="M6" t="n">
-        <v>25896</v>
+        <v>32530</v>
       </c>
       <c r="N6" t="n">
         <v>-648645</v>
       </c>
+      <c r="O6" t="n">
+        <v>16.36</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>2015</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>2.54</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="6" t="n">
         <v>47398</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>-4192</v>
       </c>
       <c r="H7" t="n">
-        <v>-2979</v>
+        <v>-7171</v>
       </c>
       <c r="I7" t="n">
         <v>2744</v>
       </c>
       <c r="J7" t="n">
-        <v>5189</v>
+        <v>7933</v>
       </c>
       <c r="K7" t="n">
         <v>942</v>
@@ -1444,11 +1452,14 @@
         <v>21635</v>
       </c>
       <c r="M7" t="n">
-        <v>85446</v>
+        <v>107081</v>
       </c>
       <c r="N7" t="n">
         <v>-6482895</v>
       </c>
+      <c r="O7" t="n">
+        <v>10.82</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1450</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>4862</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>15</v>
       </c>
       <c r="H8" t="n">
-        <v>1779</v>
+        <v>1794</v>
       </c>
       <c r="I8" t="n">
         <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1355</v>
+        <v>1359</v>
       </c>
       <c r="K8" t="n">
         <v>59</v>
@@ -1499,11 +1510,14 @@
         <v>1780</v>
       </c>
       <c r="M8" t="n">
-        <v>7888</v>
+        <v>9668</v>
       </c>
       <c r="N8" t="n">
         <v>-140150</v>
       </c>
+      <c r="O8" t="n">
+        <v>17.67</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1255</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>2.45</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="6" t="n">
         <v>3934</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>-614</v>
       </c>
       <c r="H9" t="n">
-        <v>-488</v>
+        <v>-1102</v>
       </c>
       <c r="I9" t="n">
         <v>405</v>
       </c>
       <c r="J9" t="n">
-        <v>460</v>
+        <v>865</v>
       </c>
       <c r="K9" t="n">
         <v>64</v>
@@ -1554,11 +1568,14 @@
         <v>1544</v>
       </c>
       <c r="M9" t="n">
-        <v>3869</v>
+        <v>5413</v>
       </c>
       <c r="N9" t="n">
         <v>-106280</v>
       </c>
+      <c r="O9" t="n">
+        <v>20.23</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2420</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>4.76</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>3740</v>
       </c>
       <c r="G10" s="6" t="n">
         <v>-170</v>
       </c>
       <c r="H10" t="n">
-        <v>-1365</v>
+        <v>-1535</v>
       </c>
       <c r="I10" t="n">
         <v>74</v>
       </c>
       <c r="J10" t="n">
-        <v>1492</v>
+        <v>1566</v>
       </c>
       <c r="K10" t="n">
         <v>57</v>
@@ -1609,11 +1626,14 @@
         <v>2084</v>
       </c>
       <c r="M10" t="n">
-        <v>8739</v>
+        <v>10823</v>
       </c>
       <c r="N10" t="n">
         <v>-89463</v>
       </c>
+      <c r="O10" t="n">
+        <v>25.81</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>2080</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>2.46</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>985</v>
       </c>
       <c r="G11" s="7" t="n">
         <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="I11" t="n">
         <v>-4</v>
       </c>
       <c r="J11" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="K11" t="n">
         <v>16</v>
@@ -1664,11 +1684,14 @@
         <v>4186</v>
       </c>
       <c r="M11" t="n">
-        <v>16807</v>
+        <v>20993</v>
       </c>
       <c r="N11" t="n">
         <v>-19156</v>
       </c>
+      <c r="O11" t="n">
+        <v>23.22</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>5000</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>4.93</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="7" t="n">
         <v>530</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>119</v>
       </c>
       <c r="H12" t="n">
-        <v>-112</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
         <v>-6</v>
       </c>
       <c r="J12" t="n">
-        <v>-64</v>
+        <v>-70</v>
       </c>
       <c r="K12" t="n">
         <v>19</v>
@@ -1719,11 +1742,14 @@
         <v>333</v>
       </c>
       <c r="M12" t="n">
-        <v>1399</v>
+        <v>1732</v>
       </c>
       <c r="N12" t="n">
         <v>-8884</v>
       </c>
+      <c r="O12" t="n">
+        <v>15.64</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,26 +1772,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="6" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>-52</v>
       </c>
       <c r="H13" t="n">
-        <v>-232</v>
+        <v>-284</v>
       </c>
       <c r="I13" t="n">
         <v>-70</v>
       </c>
       <c r="J13" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K13" t="n">
         <v>14</v>
@@ -1774,11 +1800,14 @@
         <v>-210</v>
       </c>
       <c r="M13" t="n">
-        <v>-70</v>
+        <v>-280</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="6" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>399</v>
       </c>
       <c r="H14" t="n">
-        <v>1025</v>
+        <v>1424</v>
       </c>
       <c r="I14" t="n">
         <v>581</v>
       </c>
       <c r="J14" t="n">
-        <v>2372</v>
+        <v>2953</v>
       </c>
       <c r="K14" t="n">
         <v>-236</v>
@@ -1829,11 +1858,14 @@
         <v>-906</v>
       </c>
       <c r="M14" t="n">
-        <v>-1755</v>
+        <v>-2661</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,20 +1888,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="7" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="7" t="n">
         <v>2060</v>
       </c>
       <c r="H15" t="n">
-        <v>7941</v>
+        <v>10001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1881,11 +1916,14 @@
         <v>-299</v>
       </c>
       <c r="M15" t="n">
-        <v>-399</v>
+        <v>-698</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1908,20 +1946,23 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="7" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>-35</v>
       </c>
       <c r="H16" t="n">
-        <v>-61</v>
+        <v>-96</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-85</v>
@@ -1933,11 +1974,14 @@
         <v>24</v>
       </c>
       <c r="M16" t="n">
-        <v>-15</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1955,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>295</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>1.03</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>1528</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>367</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>7721</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>-1</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>737</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>56</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>6510</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>31546</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-21409</v>
       </c>
-      <c r="N17" t="n">
-        <v>4.46</v>
+      <c r="O17" t="n">
+        <v>23.83</v>
       </c>
     </row>
   </sheetData>
